--- a/backend/scripts/data/ucaa-org-structure.xlsx
+++ b/backend/scripts/data/ucaa-org-structure.xlsx
@@ -7983,7 +7983,7 @@
         <v>423</v>
       </c>
       <c r="G187" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
